--- a/output/roomself_excel/13764.xlsx
+++ b/output/roomself_excel/13764.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>109928</v>
+        <v>63610</v>
       </c>
       <c r="D2" t="n">
-        <v>3089</v>
+        <v>2397</v>
       </c>
       <c r="E2" t="n">
-        <v>461</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416310</v>
+        <v>283063</v>
       </c>
       <c r="D3" t="n">
-        <v>8277</v>
+        <v>4805</v>
       </c>
       <c r="E3" t="n">
-        <v>940</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28475</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1835</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25861</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1487</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>348</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,482 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>21</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Living Room</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Bath</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C15" t="n">
         <v>57852</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D15" t="n">
         <v>2305</v>
       </c>
-      <c r="E6" t="n">
-        <v>521</v>
-      </c>
-      <c r="F6" t="n">
-        <v>419</v>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>69461</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3183</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>28475</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1835</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>109928</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3089</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25861</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1487</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>106</v>
+      </c>
+      <c r="D20" t="n">
+        <v>278</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13764.xlsx
+++ b/output/roomself_excel/13764.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,16 +449,6 @@
           <t>Perimeter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallLength</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>ExtWallWidth</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -475,12 +465,6 @@
       <c r="D2" t="n">
         <v>2397</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +481,6 @@
       <c r="D3" t="n">
         <v>4805</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +497,6 @@
       <c r="D4" t="n">
         <v>21</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -540,12 +512,6 @@
       </c>
       <c r="D5" t="n">
         <v>18</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +529,6 @@
       <c r="D6" t="n">
         <v>18</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +545,6 @@
       <c r="D7" t="n">
         <v>21</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +561,6 @@
       <c r="D8" t="n">
         <v>18</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +577,6 @@
       <c r="D9" t="n">
         <v>18</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +593,6 @@
       <c r="D10" t="n">
         <v>21</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +609,6 @@
       <c r="D11" t="n">
         <v>18</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +625,6 @@
       <c r="D12" t="n">
         <v>18</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +641,6 @@
       <c r="D13" t="n">
         <v>18</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +657,6 @@
       <c r="D14" t="n">
         <v>12</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +673,6 @@
       <c r="D15" t="n">
         <v>2305</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +689,6 @@
       <c r="D16" t="n">
         <v>3183</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +705,6 @@
       <c r="D17" t="n">
         <v>1835</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +721,6 @@
       <c r="D18" t="n">
         <v>3089</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -848,12 +736,6 @@
       </c>
       <c r="D19" t="n">
         <v>1487</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -871,12 +753,6 @@
       <c r="D20" t="n">
         <v>278</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +769,6 @@
       <c r="D21" t="n">
         <v>24</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +785,6 @@
       <c r="D22" t="n">
         <v>21</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +801,6 @@
       <c r="D23" t="n">
         <v>18</v>
       </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +817,6 @@
       <c r="D24" t="n">
         <v>18</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +833,6 @@
       <c r="D25" t="n">
         <v>15</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +849,6 @@
       <c r="D26" t="n">
         <v>12</v>
       </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1024,12 +864,6 @@
       </c>
       <c r="D27" t="n">
         <v>9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13764.xlsx
+++ b/output/roomself_excel/13764.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
